--- a/api/clv1/codelist/RegionM49.xlsx
+++ b/api/clv1/codelist/RegionM49.xlsx
@@ -1453,7 +1453,7 @@
     <t>520</t>
   </si>
   <si>
-    <t>Nauru</t>
+    <t>Naoero</t>
   </si>
   <si>
     <t>580</t>
